--- a/data/trans_orig/P15-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P15-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43512</t>
+          <t>45087</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73705</t>
+          <t>73874</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26118</t>
+          <t>24980</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48272</t>
+          <t>48522</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>77513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113350</t>
+          <t>114544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>620307</t>
+          <t>620138</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>650500</t>
+          <t>648925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>640079</t>
+          <t>639829</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>662233</t>
+          <t>663371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1269013</t>
+          <t>1267819</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1307444</t>
+          <t>1304850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68046</t>
+          <t>67180</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105488</t>
+          <t>103271</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45141</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>76092</t>
+          <t>75734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119598</t>
+          <t>121352</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168816</t>
+          <t>168693</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>856312</t>
+          <t>858529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>893754</t>
+          <t>894620</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>892301</t>
+          <t>892659</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>923252</t>
+          <t>922547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1761377</t>
+          <t>1761500</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1810595</t>
+          <t>1808841</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34118</t>
+          <t>33022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61619</t>
+          <t>62262</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24379</t>
+          <t>25004</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47014</t>
+          <t>47222</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63139</t>
+          <t>64634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99498</t>
+          <t>98512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>616890</t>
+          <t>616247</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>644391</t>
+          <t>645487</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636827</t>
+          <t>636619</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>659462</t>
+          <t>658837</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1262852</t>
+          <t>1263838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1299211</t>
+          <t>1297716</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42803</t>
+          <t>42026</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70845</t>
+          <t>71702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33788</t>
+          <t>34046</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62345</t>
+          <t>61409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82676</t>
+          <t>83572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122853</t>
+          <t>122611</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>871377</t>
+          <t>870520</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>899419</t>
+          <t>900196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>976267</t>
+          <t>977203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1004824</t>
+          <t>1004566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857981</t>
+          <t>1858223</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1898158</t>
+          <t>1897262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>213412</t>
+          <t>212290</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>272920</t>
+          <t>275280</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151081</t>
+          <t>151993</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>206321</t>
+          <t>204526</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>379017</t>
+          <t>381713</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>461354</t>
+          <t>466311</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3003623</t>
+          <t>3001263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3063131</t>
+          <t>3064253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3172876</t>
+          <t>3174671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3228116</t>
+          <t>3227204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6194387</t>
+          <t>6189430</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6276724</t>
+          <t>6274028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46634</t>
+          <t>45911</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74449</t>
+          <t>74422</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40256</t>
+          <t>40578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70644</t>
+          <t>70800</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93995</t>
+          <t>92566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133799</t>
+          <t>133754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>629020</t>
+          <t>629047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>656835</t>
+          <t>657558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>626406</t>
+          <t>626250</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>656794</t>
+          <t>656472</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1266720</t>
+          <t>1266765</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1306524</t>
+          <t>1307953</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64407</t>
+          <t>64299</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100968</t>
+          <t>100731</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60862</t>
+          <t>58206</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95608</t>
+          <t>94104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130739</t>
+          <t>131820</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>181297</t>
+          <t>183900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>916979</t>
+          <t>917216</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>953540</t>
+          <t>953648</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>936576</t>
+          <t>938080</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>971322</t>
+          <t>973978</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1868834</t>
+          <t>1866231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1919392</t>
+          <t>1918311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45698</t>
+          <t>45459</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74458</t>
+          <t>75762</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44553</t>
+          <t>44454</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75465</t>
+          <t>73721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96397</t>
+          <t>95988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>138816</t>
+          <t>136574</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>683165</t>
+          <t>681861</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>711925</t>
+          <t>712164</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>701709</t>
+          <t>703453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>732621</t>
+          <t>732720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1395981</t>
+          <t>1398223</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1438400</t>
+          <t>1438809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,75%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72822</t>
+          <t>73408</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108713</t>
+          <t>108103</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56211</t>
+          <t>57915</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91721</t>
+          <t>90304</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136562</t>
+          <t>138295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>187871</t>
+          <t>189204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>839026</t>
+          <t>839636</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>874917</t>
+          <t>874331</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>960180</t>
+          <t>961597</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>995690</t>
+          <t>993986</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1811769</t>
+          <t>1810436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1863078</t>
+          <t>1861345</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>254257</t>
+          <t>255444</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>323070</t>
+          <t>320308</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>226504</t>
+          <t>230061</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>290278</t>
+          <t>294681</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>498305</t>
+          <t>494687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>592513</t>
+          <t>591726</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3103709</t>
+          <t>3106471</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3172522</t>
+          <t>3171335</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3268031</t>
+          <t>3263628</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3331805</t>
+          <t>3328248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6392575</t>
+          <t>6393362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6486783</t>
+          <t>6490401</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30703</t>
+          <t>30149</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55103</t>
+          <t>55135</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36065</t>
+          <t>37602</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63113</t>
+          <t>65541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72952</t>
+          <t>73528</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109117</t>
+          <t>109672</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>619697</t>
+          <t>619665</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>644097</t>
+          <t>644651</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>609726</t>
+          <t>607298</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>636774</t>
+          <t>635237</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1238522</t>
+          <t>1237967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1274687</t>
+          <t>1274111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45968</t>
+          <t>45988</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77954</t>
+          <t>76885</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36123</t>
+          <t>35137</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64156</t>
+          <t>63961</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90513</t>
+          <t>89577</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130116</t>
+          <t>131548</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>944477</t>
+          <t>945546</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>976463</t>
+          <t>976443</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>978757</t>
+          <t>978952</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1006790</t>
+          <t>1007776</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1935228</t>
+          <t>1933796</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1974831</t>
+          <t>1975767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25732</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49869</t>
+          <t>50670</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21572</t>
+          <t>21556</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44207</t>
+          <t>45283</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52014</t>
+          <t>52063</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86231</t>
+          <t>86356</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>709683</t>
+          <t>708882</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>733820</t>
+          <t>733567</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>740804</t>
+          <t>739728</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>763439</t>
+          <t>763455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1458332</t>
+          <t>1458207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1492549</t>
+          <t>1492500</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45845</t>
+          <t>47011</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76484</t>
+          <t>78267</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47617</t>
+          <t>48004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80684</t>
+          <t>81212</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102384</t>
+          <t>102675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148439</t>
+          <t>148786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>861083</t>
+          <t>859300</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>891722</t>
+          <t>890556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>963095</t>
+          <t>962567</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>996162</t>
+          <t>995775</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1832907</t>
+          <t>1832560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1878962</t>
+          <t>1878671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>172348</t>
+          <t>174325</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>227456</t>
+          <t>228532</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>166967</t>
+          <t>163810</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>219653</t>
+          <t>219660</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>354579</t>
+          <t>355480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>431587</t>
+          <t>430098</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3166894</t>
+          <t>3165818</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3222002</t>
+          <t>3220025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3324889</t>
+          <t>3324882</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3377575</t>
+          <t>3380732</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6507305</t>
+          <t>6508794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6584313</t>
+          <t>6583412</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32903</t>
+          <t>32898</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60162</t>
+          <t>59971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35948</t>
+          <t>33696</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54143</t>
+          <t>53910</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74161</t>
+          <t>73527</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107718</t>
+          <t>107434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>575279</t>
+          <t>575470</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>602538</t>
+          <t>602543</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>621609</t>
+          <t>621842</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>639804</t>
+          <t>642056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1203476</t>
+          <t>1203760</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1237033</t>
+          <t>1237667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33844</t>
+          <t>32890</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95301</t>
+          <t>95332</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45025</t>
+          <t>43587</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74367</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87340</t>
+          <t>83624</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156259</t>
+          <t>157115</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1097563</t>
+          <t>1097532</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1159020</t>
+          <t>1159974</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>883739</t>
+          <t>885133</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>913081</t>
+          <t>914519</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1994712</t>
+          <t>1993856</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2063631</t>
+          <t>2067347</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20149</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41295</t>
+          <t>40861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>20940</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63580</t>
+          <t>63013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46207</t>
+          <t>48889</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91390</t>
+          <t>94430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>663385</t>
+          <t>663819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>684531</t>
+          <t>685499</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>869786</t>
+          <t>870353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>909538</t>
+          <t>912426</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1546656</t>
+          <t>1543616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1591839</t>
+          <t>1589157</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45282</t>
+          <t>44314</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76256</t>
+          <t>76077</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,44 +7618,44 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>69018</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>53516</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>85220</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>4,89%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>69018</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>54162</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>85214</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
           <t>7,78%</t>
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105226</t>
+          <t>107521</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>151761</t>
+          <t>150533</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>850575</t>
+          <t>850754</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>881549</t>
+          <t>882517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,49 +7731,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>95,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1025914</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1009712</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1041416</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>93,7%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>92,22%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>95,11%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1025914</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1009718</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1040770</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,7%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>92,22%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2396</t>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1870002</t>
+          <t>1871230</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1916537</t>
+          <t>1914242</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>156189</t>
+          <t>153650</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>237795</t>
+          <t>236555</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>177727</t>
+          <t>172841</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>248580</t>
+          <t>242043</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>354667</t>
+          <t>352614</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>462516</t>
+          <t>461129</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3222022</t>
+          <t>3223262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3303628</t>
+          <t>3306167</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3413577</t>
+          <t>3420114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3484430</t>
+          <t>3489316</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6659458</t>
+          <t>6660845</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6767307</t>
+          <t>6769360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P15-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45087</t>
+          <t>45101</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73874</t>
+          <t>72578</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24980</t>
+          <t>26010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48522</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77513</t>
+          <t>74602</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114544</t>
+          <t>112243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>620138</t>
+          <t>621434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>648925</t>
+          <t>648911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>639829</t>
+          <t>639520</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663371</t>
+          <t>662341</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1267819</t>
+          <t>1270120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1304850</t>
+          <t>1307761</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67180</t>
+          <t>67334</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103271</t>
+          <t>102608</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45846</t>
+          <t>43952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75734</t>
+          <t>75622</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121352</t>
+          <t>120843</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168693</t>
+          <t>169632</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>858529</t>
+          <t>859192</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>894620</t>
+          <t>894466</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>892659</t>
+          <t>892771</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>922547</t>
+          <t>924441</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1761500</t>
+          <t>1760561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1808841</t>
+          <t>1809350</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33022</t>
+          <t>33904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62262</t>
+          <t>62657</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25004</t>
+          <t>24750</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47222</t>
+          <t>48182</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64634</t>
+          <t>64079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98512</t>
+          <t>100496</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>616247</t>
+          <t>615852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>645487</t>
+          <t>644605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636619</t>
+          <t>635659</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>658837</t>
+          <t>659091</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1263838</t>
+          <t>1261854</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1297716</t>
+          <t>1298271</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42026</t>
+          <t>42575</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71702</t>
+          <t>71098</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,39 +1777,39 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>46347</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>34033</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>59905</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>4,46%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>46347</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34046</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>61409</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>3,28%</t>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83572</t>
+          <t>83694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122611</t>
+          <t>123918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>870520</t>
+          <t>871124</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>900196</t>
+          <t>899647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,42 +1890,42 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>95,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>992265</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>978707</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1004579</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>95,54%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>992265</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>977203</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1004566</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,54%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1858223</t>
+          <t>1856916</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1897262</t>
+          <t>1897140</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>212290</t>
+          <t>215378</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>275280</t>
+          <t>275818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151993</t>
+          <t>151737</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>204526</t>
+          <t>203313</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>381713</t>
+          <t>376930</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>466311</t>
+          <t>462125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3001263</t>
+          <t>3000725</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3064253</t>
+          <t>3061165</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3174671</t>
+          <t>3175884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3227204</t>
+          <t>3227460</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6189430</t>
+          <t>6193616</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6274028</t>
+          <t>6278811</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45911</t>
+          <t>44749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74422</t>
+          <t>73406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40578</t>
+          <t>40098</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70800</t>
+          <t>70257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92566</t>
+          <t>93170</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133754</t>
+          <t>132527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>629047</t>
+          <t>630063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>657558</t>
+          <t>658720</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>626250</t>
+          <t>626793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>656472</t>
+          <t>656952</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1266765</t>
+          <t>1267992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1307953</t>
+          <t>1307349</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64299</t>
+          <t>63619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100731</t>
+          <t>101700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58206</t>
+          <t>60634</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94104</t>
+          <t>92571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131820</t>
+          <t>131342</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183900</t>
+          <t>181648</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>917216</t>
+          <t>916247</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>953648</t>
+          <t>954328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>938080</t>
+          <t>939613</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>973978</t>
+          <t>971550</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1866231</t>
+          <t>1868483</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1918311</t>
+          <t>1918789</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45459</t>
+          <t>45135</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75762</t>
+          <t>74870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44454</t>
+          <t>43751</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73721</t>
+          <t>73380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95988</t>
+          <t>97471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136574</t>
+          <t>139391</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>681861</t>
+          <t>682753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>712164</t>
+          <t>712488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>703453</t>
+          <t>703794</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>732720</t>
+          <t>733423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1398223</t>
+          <t>1395406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1438809</t>
+          <t>1437326</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73408</t>
+          <t>72239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108103</t>
+          <t>108417</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57915</t>
+          <t>56927</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90304</t>
+          <t>88856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138295</t>
+          <t>137899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189204</t>
+          <t>186855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>839636</t>
+          <t>839322</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>874331</t>
+          <t>875500</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>961597</t>
+          <t>963045</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>993986</t>
+          <t>994974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1810436</t>
+          <t>1812785</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1861345</t>
+          <t>1861741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>255444</t>
+          <t>253974</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>320308</t>
+          <t>325624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>230061</t>
+          <t>225598</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>294681</t>
+          <t>290532</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>494687</t>
+          <t>499453</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>591726</t>
+          <t>596415</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3106471</t>
+          <t>3101155</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3171335</t>
+          <t>3172805</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3263628</t>
+          <t>3267777</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3328248</t>
+          <t>3332711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6393362</t>
+          <t>6388673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6490401</t>
+          <t>6485635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30149</t>
+          <t>30970</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55135</t>
+          <t>54298</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37602</t>
+          <t>34706</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65541</t>
+          <t>64270</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73528</t>
+          <t>73788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109672</t>
+          <t>110902</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>619665</t>
+          <t>620502</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>644651</t>
+          <t>643830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>607298</t>
+          <t>608569</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>635237</t>
+          <t>638133</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1237967</t>
+          <t>1236737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1274111</t>
+          <t>1273851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45988</t>
+          <t>46754</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76885</t>
+          <t>78778</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35137</t>
+          <t>35644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63961</t>
+          <t>63921</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89577</t>
+          <t>90305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131548</t>
+          <t>132470</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>945546</t>
+          <t>943653</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>976443</t>
+          <t>975677</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>978952</t>
+          <t>978992</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1007776</t>
+          <t>1007269</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1933796</t>
+          <t>1932874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1975767</t>
+          <t>1975039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25985</t>
+          <t>26706</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50670</t>
+          <t>49567</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,82 +5328,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>31561</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>20317</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>44012</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>68227</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>52842</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>86124</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>3,42%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>31561</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>21556</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>45283</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>68227</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>52063</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>86356</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>708882</t>
+          <t>709985</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>733567</t>
+          <t>732846</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,82 +5441,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>96,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>753450</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>740999</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>764694</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,39%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1476336</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1458439</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1491721</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>94,42%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>96,58%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>753450</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>739728</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>763455</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,98%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>94,23%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,25%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1476336</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1458207</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1492500</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>95,58%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>94,41%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47011</t>
+          <t>46403</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78267</t>
+          <t>76656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48004</t>
+          <t>47697</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81212</t>
+          <t>81024</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>102675</t>
+          <t>102915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148786</t>
+          <t>149238</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>859300</t>
+          <t>860911</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>890556</t>
+          <t>891164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>962567</t>
+          <t>962755</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>995775</t>
+          <t>996082</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1832560</t>
+          <t>1832108</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1878671</t>
+          <t>1878431</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>174325</t>
+          <t>171341</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>228532</t>
+          <t>229041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163810</t>
+          <t>165479</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>219660</t>
+          <t>222649</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>355480</t>
+          <t>353845</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>430098</t>
+          <t>430711</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3165818</t>
+          <t>3165309</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3220025</t>
+          <t>3223009</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3324882</t>
+          <t>3321893</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3380732</t>
+          <t>3379063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6508794</t>
+          <t>6508181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6583412</t>
+          <t>6585047</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>49691</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32898</t>
+          <t>37816</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59971</t>
+          <t>67051</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,17 +6604,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33696</t>
+          <t>36840</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53910</t>
+          <t>58148</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>88123</t>
+          <t>96612</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73527</t>
+          <t>81358</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107434</t>
+          <t>116136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>590560</t>
+          <t>641019</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>575470</t>
+          <t>623659</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>602543</t>
+          <t>652894</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,17 +6717,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>632510</t>
+          <t>686191</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>621842</t>
+          <t>674965</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>642056</t>
+          <t>696273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1223071</t>
+          <t>1327211</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1203760</t>
+          <t>1307687</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1237667</t>
+          <t>1342465</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1311194</t>
+          <t>1423823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>74814</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>57341</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95332</t>
+          <t>96898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57234</t>
+          <t>62804</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43587</t>
+          <t>48648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72973</t>
+          <t>79022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>124293</t>
+          <t>137618</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83624</t>
+          <t>113075</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157115</t>
+          <t>164723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1125805</t>
+          <t>974103</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1097532</t>
+          <t>952019</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1159974</t>
+          <t>991576</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>900872</t>
+          <t>1008034</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>885133</t>
+          <t>991816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>914519</t>
+          <t>1022190</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2026678</t>
+          <t>1982137</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1993856</t>
+          <t>1955032</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2067347</t>
+          <t>2006680</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40861</t>
+          <t>46218</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44108</t>
+          <t>49481</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>39120</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63013</t>
+          <t>62672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>73342</t>
+          <t>82453</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48889</t>
+          <t>65038</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94430</t>
+          <t>99197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>675446</t>
+          <t>770101</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>663819</t>
+          <t>756855</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>685499</t>
+          <t>780825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>889258</t>
+          <t>762778</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>870353</t>
+          <t>749587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>912426</t>
+          <t>773139</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1564704</t>
+          <t>1532879</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1543616</t>
+          <t>1516135</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1589157</t>
+          <t>1550294</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58885</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44314</t>
+          <t>47833</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76077</t>
+          <t>81087</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>69018</t>
+          <t>72973</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53516</t>
+          <t>58933</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85220</t>
+          <t>87421</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>127903</t>
+          <t>136520</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107521</t>
+          <t>116558</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>150533</t>
+          <t>157799</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>867946</t>
+          <t>926516</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>850754</t>
+          <t>908975</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882517</t>
+          <t>942229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1025914</t>
+          <t>1046068</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1009712</t>
+          <t>1031620</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1041416</t>
+          <t>1060108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1893860</t>
+          <t>1972584</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1871230</t>
+          <t>1951305</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1914242</t>
+          <t>1992546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>200059</t>
+          <t>221023</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153650</t>
+          <t>190405</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>236555</t>
+          <t>255818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172841</t>
+          <t>207634</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>242043</t>
+          <t>261005</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>413662</t>
+          <t>453203</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>352614</t>
+          <t>414681</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>461129</t>
+          <t>500325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3259758</t>
+          <t>3311739</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3223262</t>
+          <t>3276944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3306167</t>
+          <t>3342357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3448554</t>
+          <t>3503071</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3420114</t>
+          <t>3474246</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3489316</t>
+          <t>3527617</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6708312</t>
+          <t>6814810</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6660845</t>
+          <t>6767688</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6769360</t>
+          <t>6853332</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3662157</t>
+          <t>3735251</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7121974</t>
+          <t>7268013</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
